--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -397,91 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Test ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Module</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Test Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Failure Reason</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Actual Result</v>
+        <v>Info</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC_M_AUTH_010</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Authentication</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Verify Authentication - OAuth SSO Login Provider Token Handshake (#10)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>MEDIUM</v>
-      </c>
-      <c r="E2" t="str">
-        <v>OTP validation mismatch</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Assertion failure: Expected view element state match but encountered: OTP validation mismatch</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>TC_M_FORM_008</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Forms</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Verify Forms - Checkbox Multi-Select Group Validation (#8)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CRITICAL</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Validation message missing</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Assertion failure: Expected view element state match but encountered: Validation message missing</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TC_M_UPLD_002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>File Upload</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Verify File Upload - Upload Blueprint PDF Document (#2)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>MEDIUM</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Application crash during large file payload</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Assertion failure: Expected view element state match but encountered: Application crash during large file payload</v>
+        <v>No failures recorded</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>